--- a/assets/Shots.xlsx
+++ b/assets/Shots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3kab\Desktop\Closet\Programming\FRC\Robot2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E492266F-A62B-472F-8ACE-678BD22C6461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A799A3F-E5DA-4D30-AF79-2915798C286A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{DD05BFB3-854D-49BD-B644-2C8DC8C074CC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Distance</t>
   </si>
@@ -54,6 +54,18 @@
   </si>
   <si>
     <t>End</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Dist</t>
+  </si>
+  <si>
+    <t>Adj</t>
+  </si>
+  <si>
+    <t>Adj*1.5</t>
   </si>
 </sst>
 </file>
@@ -89,8 +101,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,10 +438,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E65753-A94A-4573-B23A-60FB6E999F55}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -448,7 +461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1.5</v>
       </c>
@@ -459,7 +472,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <f>F2-E2</f>
+        <f t="shared" ref="D2:D15" si="0">F2-E2</f>
         <v>0.8199999999999994</v>
       </c>
       <c r="E2">
@@ -469,7 +482,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1.8839999999999999</v>
       </c>
@@ -480,7 +493,7 @@
         <v>3.09</v>
       </c>
       <c r="D3">
-        <f>F3-E3</f>
+        <f t="shared" si="0"/>
         <v>1.17</v>
       </c>
       <c r="E3">
@@ -490,7 +503,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2.33</v>
       </c>
@@ -501,7 +514,7 @@
         <v>5.09</v>
       </c>
       <c r="D4">
-        <f>F4-E4</f>
+        <f t="shared" si="0"/>
         <v>1.08</v>
       </c>
       <c r="E4">
@@ -511,7 +524,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3.05</v>
       </c>
@@ -522,7 +535,7 @@
         <v>6.13</v>
       </c>
       <c r="D5">
-        <f>F5-E5</f>
+        <f t="shared" si="0"/>
         <v>1.2699999999999996</v>
       </c>
       <c r="E5">
@@ -532,7 +545,7 @@
         <v>13.67</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>3.827</v>
       </c>
@@ -543,7 +556,7 @@
         <v>5.17</v>
       </c>
       <c r="D6">
-        <f>F6-E6</f>
+        <f t="shared" si="0"/>
         <v>1.44</v>
       </c>
       <c r="E6">
@@ -553,7 +566,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5.28</v>
       </c>
@@ -564,7 +577,7 @@
         <v>13.86</v>
       </c>
       <c r="D7">
-        <f>F7-E7</f>
+        <f t="shared" si="0"/>
         <v>1.2300000000000004</v>
       </c>
       <c r="E7">
@@ -574,52 +587,118 @@
         <v>13.06</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:15">
       <c r="D8">
-        <f>F8-E8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:15">
       <c r="D9">
-        <f>F9-E9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="I9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="D10">
-        <f>F10-E10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="I10" s="1">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1">
+        <v>12</v>
+      </c>
+      <c r="K10" s="1">
+        <f>I10+(J10-I10)</f>
+        <v>12</v>
+      </c>
+      <c r="L10" s="1">
+        <f>I10-((K10-J10))</f>
+        <v>5</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="D11">
-        <f>F11-E11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="K11" s="1">
+        <f>J10-I10</f>
+        <v>7</v>
+      </c>
+      <c r="L11">
+        <f>O10*2</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="D12">
-        <f>F12-E12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:15">
+      <c r="A13">
+        <v>1.8</v>
+      </c>
       <c r="D13">
-        <f>F13-E13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <f t="shared" si="0"/>
+        <v>0.97</v>
+      </c>
+      <c r="E13">
+        <v>0.8</v>
+      </c>
+      <c r="F13">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14">
+        <v>3.1749999999999998</v>
+      </c>
       <c r="D14">
-        <f>F14-E14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <f t="shared" si="0"/>
+        <v>1.3400000000000003</v>
+      </c>
+      <c r="E14">
+        <v>1.63</v>
+      </c>
+      <c r="F14">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15">
+        <v>4.7779999999999996</v>
+      </c>
       <c r="D15">
-        <f>F15-E15</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="E15">
+        <v>1.69</v>
+      </c>
+      <c r="F15">
+        <v>3.24</v>
       </c>
     </row>
   </sheetData>
@@ -627,5 +706,6 @@
     <sortCondition ref="A1:A15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>